--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,320 +1091,75 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Knowledge Graph Developer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>United Airlines</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Launch Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Power BI Consultant</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,54 +671,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior AWS / Amazon Connect Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,46 +727,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,390 +776,40 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Development Engineer I</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Development Engineer I</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bethpage, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Machine Learning Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Launch Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Power BI Consultant</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,25 +688,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,32 +618,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Senior AWS / Amazon Connect Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS / Amazon Connect Engineer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,85 +731,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Power BI Consultant</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,77 +468,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,24 +556,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,32 +583,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AWS / Amazon Connect Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AWS / Amazon Connect Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,87 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Power BI Consultant</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,32 +548,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AWS / Amazon Connect Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AWS / Amazon Connect Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,50 +626,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,41 +602,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Sr Java Developer with E-Trading exp must</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=b93bfb157e46dad0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AWS / Amazon Connect Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,15 +591,50 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior AWS / Amazon Connect Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
         </is>

--- a/results/job_matches_2026-08-02.xlsx
+++ b/results/job_matches_2026-08-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>QA &amp; Operations Engineer – Amazon Connect (CCaaS)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=94e45a080aab120d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AWS / Amazon Connect Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,15 +626,85 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rocklin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, HDFS, MapReduce, Spark, Scala, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e235cc7e99c3a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior AWS / Amazon Connect Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=adf03900850392a3</t>
         </is>
